--- a/data/bc_seafood_production_23-24.xlsx
+++ b/data/bc_seafood_production_23-24.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JVIEIRA\Downloads\data catalogue\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ubcca-my.sharepoint.com/personal/haley_oleynik_ubc_ca/Documents/Documents/GitHub/Fraser_salmon_retrospective-analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A457C650-4D6E-46D5-8063-F7C44E9D2737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{A457C650-4D6E-46D5-8063-F7C44E9D2737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D44C1EF-3D44-41A8-B065-49565832F014}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-52920" yWindow="-2610" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA" sheetId="1" r:id="rId1"/>
     <sheet name="notes" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DATA!$A$1:$H$71</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -25,16 +28,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="53">
   <si>
     <t>Farmed</t>
   </si>
@@ -187,14 +191,21 @@
   </si>
   <si>
     <t>Farmed Other includes arctic char, barramundi, rainbow trout, tilapia.</t>
+  </si>
+  <si>
+    <t>landed value / kg</t>
+  </si>
+  <si>
+    <t>wholesale value / kg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -210,12 +221,18 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -245,7 +262,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -264,6 +281,15 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -566,16 +592,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F71"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="25.81640625" customWidth="1"/>
     <col min="4" max="4" width="23.26953125" style="3" customWidth="1"/>
     <col min="5" max="5" width="14.81640625" style="7" customWidth="1"/>
     <col min="6" max="6" width="19.6328125" style="7" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="8" width="14.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
@@ -594,8 +623,14 @@
       <c r="F1" s="6" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2023</v>
       </c>
@@ -614,8 +649,16 @@
       <c r="F2" s="7">
         <v>553309948.01999998</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G2" s="8">
+        <f>E2/D2</f>
+        <v>9.7518027933845488</v>
+      </c>
+      <c r="H2" s="8">
+        <f>F2/D2</f>
+        <v>11.63333279435002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2023</v>
       </c>
@@ -634,8 +677,16 @@
       <c r="F3" s="7">
         <v>16644111</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G3" s="8">
+        <f t="shared" ref="G3:G66" si="0">E3/D3</f>
+        <v>9.4200663250235941</v>
+      </c>
+      <c r="H3" s="8">
+        <f t="shared" ref="H3:H66" si="1">F3/D3</f>
+        <v>11.859962231530119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2023</v>
       </c>
@@ -654,8 +705,16 @@
       <c r="F4" s="7">
         <v>8491633</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G4" s="8">
+        <f t="shared" si="0"/>
+        <v>6.1561947539777737</v>
+      </c>
+      <c r="H4" s="8">
+        <f t="shared" si="1"/>
+        <v>11.843624209378573</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2023</v>
       </c>
@@ -674,8 +733,16 @@
       <c r="F5" s="7">
         <v>51357108.899999999</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G5" s="8">
+        <f t="shared" si="0"/>
+        <v>14.288510088974798</v>
+      </c>
+      <c r="H5" s="8">
+        <f t="shared" si="1"/>
+        <v>39.252520540550705</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2023</v>
       </c>
@@ -694,8 +761,16 @@
       <c r="F6" s="7">
         <v>22615750</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G6" s="8">
+        <f t="shared" si="0"/>
+        <v>2.1845089658160344</v>
+      </c>
+      <c r="H6" s="8">
+        <f t="shared" si="1"/>
+        <v>3.0680861751272306</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2023</v>
       </c>
@@ -714,8 +789,16 @@
       <c r="F7" s="7">
         <v>44114636</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G7" s="8">
+        <f t="shared" si="0"/>
+        <v>16.176322522262865</v>
+      </c>
+      <c r="H7" s="8">
+        <f t="shared" si="1"/>
+        <v>17.624075897975494</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2023</v>
       </c>
@@ -734,8 +817,16 @@
       <c r="F8" s="7">
         <v>3924388</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G8" s="8">
+        <f t="shared" si="0"/>
+        <v>11.980290010034356</v>
+      </c>
+      <c r="H8" s="8">
+        <f t="shared" si="1"/>
+        <v>40.857578918007903</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2023</v>
       </c>
@@ -754,48 +845,72 @@
       <c r="F9" s="7">
         <v>4324818</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>2023</v>
-      </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="G9" s="8">
+        <f t="shared" si="0"/>
+        <v>330.69397397598487</v>
+      </c>
+      <c r="H9" s="8">
+        <f t="shared" si="1"/>
+        <v>1258.591719603322</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="13">
+        <v>2023</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="14">
         <v>1486.4821085584999</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="15">
         <v>11027132.374535751</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="15">
         <v>21545145.350000001</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>2023</v>
-      </c>
-      <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="G10" s="16">
+        <f t="shared" si="0"/>
+        <v>7418.2745362668329</v>
+      </c>
+      <c r="H10" s="16">
+        <f t="shared" si="1"/>
+        <v>14494.049558990773</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="9">
+        <v>2023</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="10">
         <v>485.41812637534878</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="11">
         <v>1247682.9849467271</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="11">
         <v>8486750.9100000001</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G11" s="12">
+        <f t="shared" si="0"/>
+        <v>2570.3263169491906</v>
+      </c>
+      <c r="H11" s="12">
+        <f t="shared" si="1"/>
+        <v>17483.382776352348</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2023</v>
       </c>
@@ -814,28 +929,44 @@
       <c r="F12" s="7">
         <v>12615274.5</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>2023</v>
-      </c>
-      <c r="B13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="G12" s="8">
+        <f t="shared" si="0"/>
+        <v>6383.8598347242232</v>
+      </c>
+      <c r="H12" s="8">
+        <f t="shared" si="1"/>
+        <v>46720.855369361416</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="13">
+        <v>2023</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="14">
         <v>518.83008102422423</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="15">
         <v>2663207.459535569</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="15">
         <v>26072401.09</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G13" s="16">
+        <f t="shared" si="0"/>
+        <v>5133.1014853227516</v>
+      </c>
+      <c r="H13" s="16">
+        <f t="shared" si="1"/>
+        <v>50252.292693843781</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2023</v>
       </c>
@@ -854,8 +985,16 @@
       <c r="F14" s="7">
         <v>230911113.56999999</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G14" s="8">
+        <f t="shared" si="0"/>
+        <v>15809.238119274234</v>
+      </c>
+      <c r="H14" s="8">
+        <f t="shared" si="1"/>
+        <v>32152.167753832906</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2023</v>
       </c>
@@ -874,8 +1013,16 @@
       <c r="F15" s="7">
         <v>71206281</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G15" s="8">
+        <f t="shared" si="0"/>
+        <v>44864.064868183508</v>
+      </c>
+      <c r="H15" s="8">
+        <f t="shared" si="1"/>
+        <v>49299.16274973673</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2023</v>
       </c>
@@ -894,8 +1041,16 @@
       <c r="F16" s="7">
         <v>34947474</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G16" s="8">
+        <f t="shared" si="0"/>
+        <v>815.709399999997</v>
+      </c>
+      <c r="H16" s="8">
+        <f t="shared" si="1"/>
+        <v>1152.9911512060733</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2023</v>
       </c>
@@ -914,8 +1069,16 @@
       <c r="F17" s="7">
         <v>61691439.259999998</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G17" s="8">
+        <f t="shared" si="0"/>
+        <v>16957.139040948543</v>
+      </c>
+      <c r="H17" s="8">
+        <f t="shared" si="1"/>
+        <v>19499.828414047679</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2023</v>
       </c>
@@ -934,8 +1097,16 @@
       <c r="F18" s="7">
         <v>34685178.359999999</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G18" s="8">
+        <f t="shared" si="0"/>
+        <v>701.93843816907838</v>
+      </c>
+      <c r="H18" s="8">
+        <f t="shared" si="1"/>
+        <v>7316.1920558819138</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2023</v>
       </c>
@@ -954,8 +1125,16 @@
       <c r="F19" s="7">
         <v>13457191.34</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G19" s="8">
+        <f t="shared" si="0"/>
+        <v>4893.1657802369637</v>
+      </c>
+      <c r="H19" s="8">
+        <f t="shared" si="1"/>
+        <v>6586.5016127938516</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2023</v>
       </c>
@@ -974,8 +1153,16 @@
       <c r="F20" s="7">
         <v>156009620.56</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G20" s="8">
+        <f t="shared" si="0"/>
+        <v>1298.8545488076561</v>
+      </c>
+      <c r="H20" s="8">
+        <f t="shared" si="1"/>
+        <v>94250.723544710927</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2023</v>
       </c>
@@ -994,8 +1181,16 @@
       <c r="F21" s="7">
         <v>9100430.1600000001</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G21" s="8">
+        <f t="shared" si="0"/>
+        <v>1328.2475487422601</v>
+      </c>
+      <c r="H21" s="8">
+        <f t="shared" si="1"/>
+        <v>49475.522598562136</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2023</v>
       </c>
@@ -1014,8 +1209,16 @@
       <c r="F22" s="7">
         <v>24395047.260000002</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G22" s="8">
+        <f t="shared" si="0"/>
+        <v>8467.44390334522</v>
+      </c>
+      <c r="H22" s="8">
+        <f t="shared" si="1"/>
+        <v>399735.32247492956</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2023</v>
       </c>
@@ -1034,8 +1237,16 @@
       <c r="F23" s="7">
         <v>8445764.6999999993</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G23" s="8">
+        <f t="shared" si="0"/>
+        <v>1544.1165576431163</v>
+      </c>
+      <c r="H23" s="8">
+        <f t="shared" si="1"/>
+        <v>14253.36976870217</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2023</v>
       </c>
@@ -1054,8 +1265,16 @@
       <c r="F24" s="7">
         <v>18139952.699999999</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G24" s="8">
+        <f t="shared" si="0"/>
+        <v>569.54764285558554</v>
+      </c>
+      <c r="H24" s="8">
+        <f t="shared" si="1"/>
+        <v>5090.5464877945778</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2023</v>
       </c>
@@ -1074,8 +1293,16 @@
       <c r="F25" s="7">
         <v>7642580</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G25" s="8">
+        <f t="shared" si="0"/>
+        <v>440.92397015646998</v>
+      </c>
+      <c r="H25" s="8">
+        <f t="shared" si="1"/>
+        <v>1298.1778239790431</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2023</v>
       </c>
@@ -1094,8 +1321,16 @@
       <c r="F26" s="7">
         <v>82728000</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G26" s="8">
+        <f t="shared" si="0"/>
+        <v>45415.220935025878</v>
+      </c>
+      <c r="H26" s="8">
+        <f t="shared" si="1"/>
+        <v>51817.573678817236</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2023</v>
       </c>
@@ -1114,8 +1349,16 @@
       <c r="F27" s="7">
         <v>37668055.369999997</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G27" s="8">
+        <f t="shared" si="0"/>
+        <v>1289.7056857536945</v>
+      </c>
+      <c r="H27" s="8">
+        <f t="shared" si="1"/>
+        <v>1950.7574376618309</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2023</v>
       </c>
@@ -1134,8 +1377,16 @@
       <c r="F28" s="7">
         <v>20852959.57</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G28" s="8">
+        <f t="shared" si="0"/>
+        <v>7706.3201026038578</v>
+      </c>
+      <c r="H28" s="8">
+        <f t="shared" si="1"/>
+        <v>6216.8623630094889</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2023</v>
       </c>
@@ -1154,8 +1405,16 @@
       <c r="F29" s="7">
         <v>15762078</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G29" s="8">
+        <f t="shared" si="0"/>
+        <v>5158.8162751869777</v>
+      </c>
+      <c r="H29" s="8">
+        <f t="shared" si="1"/>
+        <v>9541.606875283951</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2023</v>
       </c>
@@ -1174,8 +1433,16 @@
       <c r="F30" s="7">
         <v>2637736</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G30" s="8">
+        <f t="shared" si="0"/>
+        <v>6172.9422395060628</v>
+      </c>
+      <c r="H30" s="8">
+        <f t="shared" si="1"/>
+        <v>8843.8243102219658</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2023</v>
       </c>
@@ -1194,8 +1461,16 @@
       <c r="F31" s="7">
         <v>23538447.100000001</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G31" s="8">
+        <f t="shared" si="0"/>
+        <v>3086.4712749878727</v>
+      </c>
+      <c r="H31" s="8">
+        <f t="shared" si="1"/>
+        <v>11881.803639484113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2023</v>
       </c>
@@ -1214,8 +1489,16 @@
       <c r="F32" s="7">
         <v>1421281.22</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G32" s="8">
+        <f t="shared" si="0"/>
+        <v>9973.8190349018514</v>
+      </c>
+      <c r="H32" s="8">
+        <f t="shared" si="1"/>
+        <v>17652.597312268674</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2023</v>
       </c>
@@ -1234,28 +1517,44 @@
       <c r="F33" s="7">
         <v>488292</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34">
-        <v>2023</v>
-      </c>
-      <c r="B34" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="G33" s="8">
+        <f t="shared" si="0"/>
+        <v>1212.540999999999</v>
+      </c>
+      <c r="H33" s="8">
+        <f t="shared" si="1"/>
+        <v>1666.4975568841112</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34" s="13">
+        <v>2023</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="14">
         <v>1212.5930230872559</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="15">
         <v>6418695.0162571371</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34" s="15">
         <v>154399578.5</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G34" s="16">
+        <f t="shared" si="0"/>
+        <v>5293.3629783842653</v>
+      </c>
+      <c r="H34" s="16">
+        <f t="shared" si="1"/>
+        <v>127330.08978304974</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2023</v>
       </c>
@@ -1274,8 +1573,16 @@
       <c r="F35" s="7">
         <v>7064900</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G35" s="8">
+        <f t="shared" si="0"/>
+        <v>1290.6973315777752</v>
+      </c>
+      <c r="H35" s="8">
+        <f t="shared" si="1"/>
+        <v>2894.229964675761</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2023</v>
       </c>
@@ -1294,8 +1601,16 @@
       <c r="F36" s="7">
         <v>34142949</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G36" s="8">
+        <f t="shared" si="0"/>
+        <v>4850.1697679761564</v>
+      </c>
+      <c r="H36" s="8">
+        <f t="shared" si="1"/>
+        <v>29860.404918753815</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>2024</v>
       </c>
@@ -1314,8 +1629,16 @@
       <c r="F37" s="7">
         <v>516525613.36000001</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G37" s="8">
+        <f t="shared" si="0"/>
+        <v>9.1720823607291191</v>
+      </c>
+      <c r="H37" s="8">
+        <f t="shared" si="1"/>
+        <v>10.178645160802647</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>2024</v>
       </c>
@@ -1334,8 +1657,16 @@
       <c r="F38" s="7">
         <v>24428543.98</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G38" s="8">
+        <f t="shared" si="0"/>
+        <v>9.0406356374973207</v>
+      </c>
+      <c r="H38" s="8">
+        <f t="shared" si="1"/>
+        <v>13.6011781394955</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>2024</v>
       </c>
@@ -1354,8 +1685,16 @@
       <c r="F39" s="7">
         <v>6332457.1699999999</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G39" s="8">
+        <f t="shared" si="0"/>
+        <v>6.6667756163738146</v>
+      </c>
+      <c r="H39" s="8">
+        <f t="shared" si="1"/>
+        <v>13.451922943584204</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>2024</v>
       </c>
@@ -1374,8 +1713,16 @@
       <c r="F40" s="7">
         <v>36478950.270000003</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G40" s="8">
+        <f t="shared" si="0"/>
+        <v>16.277853192691602</v>
+      </c>
+      <c r="H40" s="8">
+        <f t="shared" si="1"/>
+        <v>45.552721773475071</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>2024</v>
       </c>
@@ -1394,8 +1741,16 @@
       <c r="F41" s="7">
         <v>29228705.120000001</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G41" s="8">
+        <f t="shared" si="0"/>
+        <v>2.224738105348639</v>
+      </c>
+      <c r="H41" s="8">
+        <f t="shared" si="1"/>
+        <v>4.0619829884306933</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>2024</v>
       </c>
@@ -1414,8 +1769,16 @@
       <c r="F42" s="7">
         <v>78755482.299999997</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G42" s="8">
+        <f t="shared" si="0"/>
+        <v>15.755196377820667</v>
+      </c>
+      <c r="H42" s="8">
+        <f t="shared" si="1"/>
+        <v>25.653460467919118</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2024</v>
       </c>
@@ -1434,8 +1797,16 @@
       <c r="F43" s="7">
         <v>4761407.25</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G43" s="8">
+        <f t="shared" si="0"/>
+        <v>7.7661063618852895</v>
+      </c>
+      <c r="H43" s="8">
+        <f t="shared" si="1"/>
+        <v>63.771406779992859</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>2024</v>
       </c>
@@ -1454,48 +1825,72 @@
       <c r="F44" s="7">
         <v>2354353.4900000002</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45">
-        <v>2024</v>
-      </c>
-      <c r="B45" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="G44" s="8">
+        <f t="shared" si="0"/>
+        <v>220.46584734374804</v>
+      </c>
+      <c r="H44" s="8">
+        <f t="shared" si="1"/>
+        <v>619.3847913216058</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A45" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="14">
         <v>1405.5379185013451</v>
       </c>
-      <c r="E45" s="7">
+      <c r="E45" s="15">
         <v>14046530.6265535</v>
       </c>
-      <c r="F45" s="7">
+      <c r="F45" s="15">
         <v>21873172.829999998</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46">
-        <v>2024</v>
-      </c>
-      <c r="B46" t="s">
-        <v>8</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="G45" s="16">
+        <f t="shared" si="0"/>
+        <v>9993.7045039173427</v>
+      </c>
+      <c r="H45" s="16">
+        <f t="shared" si="1"/>
+        <v>15562.136419145683</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A46" s="9">
+        <v>2024</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="10">
         <v>1840.5923763752421</v>
       </c>
-      <c r="E46" s="7">
+      <c r="E46" s="11">
         <v>5307168.9457571078</v>
       </c>
-      <c r="F46" s="7">
+      <c r="F46" s="11">
         <v>20094200.77</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G46" s="12">
+        <f t="shared" si="0"/>
+        <v>2883.4026555128648</v>
+      </c>
+      <c r="H46" s="12">
+        <f t="shared" si="1"/>
+        <v>10917.246549489884</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>2024</v>
       </c>
@@ -1514,28 +1909,44 @@
       <c r="F47" s="7">
         <v>5408898.5</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48">
-        <v>2024</v>
-      </c>
-      <c r="B48" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="G47" s="8">
+        <f t="shared" si="0"/>
+        <v>6861.0354178219222</v>
+      </c>
+      <c r="H47" s="8">
+        <f t="shared" si="1"/>
+        <v>13939.048733075741</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A48" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="14">
         <v>432.37594046442018</v>
       </c>
-      <c r="E48" s="7">
+      <c r="E48" s="15">
         <v>1829941.1917179711</v>
       </c>
-      <c r="F48" s="7">
+      <c r="F48" s="15">
         <v>19979898.809999999</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G48" s="16">
+        <f t="shared" si="0"/>
+        <v>4232.2919026262407</v>
+      </c>
+      <c r="H48" s="16">
+        <f t="shared" si="1"/>
+        <v>46209.55270670091</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>2024</v>
       </c>
@@ -1554,8 +1965,16 @@
       <c r="F49" s="7">
         <v>177924993.34999999</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G49" s="8">
+        <f t="shared" si="0"/>
+        <v>18967.38161771755</v>
+      </c>
+      <c r="H49" s="8">
+        <f t="shared" si="1"/>
+        <v>39902.07610784471</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>2024</v>
       </c>
@@ -1574,8 +1993,16 @@
       <c r="F50" s="7">
         <v>47424410.060000002</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G50" s="8">
+        <f t="shared" si="0"/>
+        <v>43761.753995491978</v>
+      </c>
+      <c r="H50" s="8">
+        <f t="shared" si="1"/>
+        <v>44767.461235663388</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>2024</v>
       </c>
@@ -1594,8 +2021,16 @@
       <c r="F51" s="7">
         <v>10515542.560000001</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G51" s="8">
+        <f t="shared" si="0"/>
+        <v>371.43883733152188</v>
+      </c>
+      <c r="H51" s="8">
+        <f t="shared" si="1"/>
+        <v>850.50023919742182</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>2024</v>
       </c>
@@ -1614,8 +2049,16 @@
       <c r="F52" s="7">
         <v>68540969.799999997</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G52" s="8">
+        <f t="shared" si="0"/>
+        <v>16298.209519735017</v>
+      </c>
+      <c r="H52" s="8">
+        <f t="shared" si="1"/>
+        <v>24401.528859825252</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>2024</v>
       </c>
@@ -1634,8 +2077,16 @@
       <c r="F53" s="7">
         <v>17353515.370000001</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G53" s="8">
+        <f t="shared" si="0"/>
+        <v>1097.0298509857946</v>
+      </c>
+      <c r="H53" s="8">
+        <f t="shared" si="1"/>
+        <v>3038.7079097822702</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>2024</v>
       </c>
@@ -1654,8 +2105,16 @@
       <c r="F54" s="7">
         <v>12751988.939999999</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G54" s="8">
+        <f t="shared" si="0"/>
+        <v>4588.0678732764836</v>
+      </c>
+      <c r="H54" s="8">
+        <f t="shared" si="1"/>
+        <v>8262.8600396000747</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>2024</v>
       </c>
@@ -1674,8 +2133,16 @@
       <c r="F55" s="7">
         <v>132574121.87</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G55" s="8">
+        <f t="shared" si="0"/>
+        <v>480.61698681112478</v>
+      </c>
+      <c r="H55" s="8">
+        <f t="shared" si="1"/>
+        <v>101371.36183791439</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>2024</v>
       </c>
@@ -1694,8 +2161,16 @@
       <c r="F56" s="7">
         <v>12832294.630000001</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G56" s="8">
+        <f t="shared" si="0"/>
+        <v>436.40770797468923</v>
+      </c>
+      <c r="H56" s="8">
+        <f t="shared" si="1"/>
+        <v>77863.781861177151</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>2024</v>
       </c>
@@ -1714,8 +2189,16 @@
       <c r="F57" s="7">
         <v>7006812.7100000009</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G57" s="8">
+        <f t="shared" si="0"/>
+        <v>6455.8594874678647</v>
+      </c>
+      <c r="H57" s="8">
+        <f t="shared" si="1"/>
+        <v>110033.33453728863</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>2024</v>
       </c>
@@ -1734,8 +2217,16 @@
       <c r="F58" s="7">
         <v>3345832.33</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G58" s="8">
+        <f t="shared" si="0"/>
+        <v>1652.7352139141785</v>
+      </c>
+      <c r="H58" s="8">
+        <f t="shared" si="1"/>
+        <v>6757.3543886298366</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>2024</v>
       </c>
@@ -1754,8 +2245,16 @@
       <c r="F59" s="7">
         <v>15182749.77</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G59" s="8">
+        <f t="shared" si="0"/>
+        <v>750.2027221935831</v>
+      </c>
+      <c r="H59" s="8">
+        <f t="shared" si="1"/>
+        <v>4148.9544352247185</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>2024</v>
       </c>
@@ -1774,8 +2273,16 @@
       <c r="F60" s="7">
         <v>20189800.719999999</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G60" s="8">
+        <f t="shared" si="0"/>
+        <v>220.46200000000002</v>
+      </c>
+      <c r="H60" s="8">
+        <f t="shared" si="1"/>
+        <v>2222.3249102766536</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>2024</v>
       </c>
@@ -1794,8 +2301,16 @@
       <c r="F61" s="7">
         <v>73429462.549999997</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G61" s="8">
+        <f t="shared" si="0"/>
+        <v>41446.893392684411</v>
+      </c>
+      <c r="H61" s="8">
+        <f t="shared" si="1"/>
+        <v>44080.546517533294</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>2024</v>
       </c>
@@ -1814,8 +2329,16 @@
       <c r="F62" s="7">
         <v>17204438.789999999</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G62" s="8">
+        <f t="shared" si="0"/>
+        <v>1032.2970382898354</v>
+      </c>
+      <c r="H62" s="8">
+        <f t="shared" si="1"/>
+        <v>1086.0008533688656</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>2024</v>
       </c>
@@ -1834,8 +2357,16 @@
       <c r="F63" s="7">
         <v>20263030.489999998</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G63" s="8">
+        <f t="shared" si="0"/>
+        <v>8117.35074649538</v>
+      </c>
+      <c r="H63" s="8">
+        <f t="shared" si="1"/>
+        <v>8345.8459010965325</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>2024</v>
       </c>
@@ -1854,8 +2385,16 @@
       <c r="F64" s="7">
         <v>10070302</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G64" s="8">
+        <f t="shared" si="0"/>
+        <v>8002.7790924966621</v>
+      </c>
+      <c r="H64" s="8">
+        <f t="shared" si="1"/>
+        <v>6097.3580957844797</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>2024</v>
       </c>
@@ -1874,8 +2413,16 @@
       <c r="F65" s="7">
         <v>3323845</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G65" s="8">
+        <f t="shared" si="0"/>
+        <v>9369.6446539608132</v>
+      </c>
+      <c r="H65" s="8">
+        <f t="shared" si="1"/>
+        <v>9575.2443616062028</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>2024</v>
       </c>
@@ -1894,8 +2441,16 @@
       <c r="F66" s="7">
         <v>16375544.199999999</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G66" s="8">
+        <f t="shared" si="0"/>
+        <v>3637.6268744867771</v>
+      </c>
+      <c r="H66" s="8">
+        <f t="shared" si="1"/>
+        <v>8878.6124992612695</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>2024</v>
       </c>
@@ -1914,8 +2469,16 @@
       <c r="F67" s="7">
         <v>2586724.36</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G67" s="8">
+        <f t="shared" ref="G67:G71" si="2">E67/D67</f>
+        <v>10729.761844486713</v>
+      </c>
+      <c r="H67" s="8">
+        <f t="shared" ref="H67:H71" si="3">F67/D67</f>
+        <v>19588.234902124113</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>2024</v>
       </c>
@@ -1934,28 +2497,44 @@
       <c r="F68" s="7">
         <v>305382.13</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A69">
-        <v>2024</v>
-      </c>
-      <c r="B69" t="s">
-        <v>8</v>
-      </c>
-      <c r="C69" t="s">
+      <c r="G68" s="8">
+        <f t="shared" si="2"/>
+        <v>1237.2943095771711</v>
+      </c>
+      <c r="H68" s="8">
+        <f t="shared" si="3"/>
+        <v>1205.857771216994</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A69" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C69" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D69" s="3">
+      <c r="D69" s="14">
         <v>1418.832411037441</v>
       </c>
-      <c r="E69" s="7">
+      <c r="E69" s="15">
         <v>7627122.9939184003</v>
       </c>
-      <c r="F69" s="7">
+      <c r="F69" s="15">
         <v>126104037.90000001</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G69" s="16">
+        <f t="shared" si="2"/>
+        <v>5375.633467762058</v>
+      </c>
+      <c r="H69" s="16">
+        <f t="shared" si="3"/>
+        <v>88878.740659577656</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>2024</v>
       </c>
@@ -1974,8 +2553,16 @@
       <c r="F70" s="7">
         <v>4908461.72</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G70" s="8">
+        <f t="shared" si="2"/>
+        <v>1094.4858179655519</v>
+      </c>
+      <c r="H70" s="8">
+        <f t="shared" si="3"/>
+        <v>1763.7999566680719</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>2024</v>
       </c>
@@ -1994,8 +2581,26 @@
       <c r="F71" s="7">
         <v>25762136.739999998</v>
       </c>
+      <c r="G71" s="8">
+        <f t="shared" si="2"/>
+        <v>6062.712209949992</v>
+      </c>
+      <c r="H71" s="8">
+        <f t="shared" si="3"/>
+        <v>8931.4517567421844</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H71" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Chinook Salmon"/>
+        <filter val="Chum Salmon"/>
+        <filter val="Coho Salmon"/>
+        <filter val="Sockeye Salmon"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
